--- a/ML_Topics_Codes_Saifur/Linear_Regression/Simple_Linear_Regression/data_to_predict.xlsx
+++ b/ML_Topics_Codes_Saifur/Linear_Regression/Simple_Linear_Regression/data_to_predict.xlsx
@@ -275,47 +275,47 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
-        <v>4001</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
-        <v>4002</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
-        <v>2600</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
-        <v>3000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
-        <v>3600</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="n">
-        <v>4000</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
-        <v>4001</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
-        <v>4002</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="n">
-        <v>2600</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/ML_Topics_Codes_Saifur/Linear_Regression/Simple_Linear_Regression/data_to_predict.xlsx
+++ b/ML_Topics_Codes_Saifur/Linear_Regression/Simple_Linear_Regression/data_to_predict.xlsx
@@ -240,7 +240,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -286,41 +286,6 @@
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
         <v>7000</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
-        <v>3800</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
-        <v>4700</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
-        <v>5600</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
-        <v>3000</v>
       </c>
     </row>
   </sheetData>
